--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2293D86-4155-44D5-B00D-F647CB1B084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BCC3CD4-971A-4A3E-A0F6-61F1876E7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{E34FE578-96B3-492E-A6CE-C5C41AE6FF30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F818FDD4-88F0-465B-884E-5053363A6E8A}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -1393,7 +1396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7FDFEB3-DDBB-4096-9211-3C33793FF4DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F287104-4FF8-4428-BDE5-D0708DF938AC}">
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2571,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="S20" t="s">
         <v>311</v>
@@ -2630,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="S21" t="s">
         <v>311</v>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BCC3CD4-971A-4A3E-A0F6-61F1876E7430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{419DF350-278C-4352-94C4-0F80744EB451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F818FDD4-88F0-465B-884E-5053363A6E8A}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{43CF670D-C9AF-4011-B3BB-AD8B367A135A}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -1396,7 +1396,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F287104-4FF8-4428-BDE5-D0708DF938AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DE9BD8-D0E7-41D4-A330-01F3591885DA}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{419DF350-278C-4352-94C4-0F80744EB451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D1CBE00-0021-4EB2-B714-DB496B76E42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{43CF670D-C9AF-4011-B3BB-AD8B367A135A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C3A60B2D-63B0-435B-B6D3-5132FC6FB1AD}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="349">
   <si>
     <t>ID</t>
   </si>
@@ -938,45 +938,78 @@
     <t>Card_Illust_102</t>
   </si>
   <si>
+    <t>Card_Illust_103</t>
+  </si>
+  <si>
+    <t>Card_Illust_104</t>
+  </si>
+  <si>
     <t>Card_Illust_105</t>
   </si>
   <si>
+    <t>Card_Illust_106</t>
+  </si>
+  <si>
     <t>Card_Effect_107</t>
   </si>
   <si>
     <t>Card_Illust_107</t>
   </si>
   <si>
+    <t>Card_Illust_108</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel_Enhanced</t>
   </si>
   <si>
     <t>Card_Effect_109</t>
   </si>
   <si>
+    <t>Card_Illust_109</t>
+  </si>
+  <si>
     <t>Card_Cross Chisel</t>
   </si>
   <si>
+    <t>Card_Illust_110</t>
+  </si>
+  <si>
     <t>Card_Effect_111</t>
   </si>
   <si>
     <t>Card_Illust_111</t>
   </si>
   <si>
+    <t>Card_Illust_112</t>
+  </si>
+  <si>
     <t>Card_Illust_113</t>
   </si>
   <si>
+    <t>Card_Illust_114</t>
+  </si>
+  <si>
     <t>Card_Effect_115</t>
   </si>
   <si>
     <t>Card_Illust_115</t>
   </si>
   <si>
+    <t>Card_Illust_116</t>
+  </si>
+  <si>
     <t>Card_Illust_117</t>
   </si>
   <si>
+    <t>Card_Illust_118</t>
+  </si>
+  <si>
     <t>Card_Illust_119</t>
   </si>
   <si>
+    <t>Card_Illust_120</t>
+  </si>
+  <si>
     <t>Card_Large Scissors_Enhanced</t>
   </si>
   <si>
@@ -989,19 +1022,58 @@
     <t>Card_Large Scissors</t>
   </si>
   <si>
+    <t>Card_Illust_122</t>
+  </si>
+  <si>
+    <t>Card_Illust_123</t>
+  </si>
+  <si>
     <t>Card_Effect_124</t>
   </si>
   <si>
+    <t>Card_Illust_124</t>
+  </si>
+  <si>
     <t>Card_Effect_125</t>
   </si>
   <si>
+    <t>Card_Illust_125</t>
+  </si>
+  <si>
+    <t>Card_Illust_126</t>
+  </si>
+  <si>
+    <t>Card_Illust_127</t>
+  </si>
+  <si>
+    <t>Card_Illust_128</t>
+  </si>
+  <si>
     <t>Card_Adventurer'sTorch_Enhanced</t>
   </si>
   <si>
+    <t>Card_Illust_129</t>
+  </si>
+  <si>
     <t>Card_Adventurer'sTorch</t>
   </si>
   <si>
+    <t>Card_Illust_130</t>
+  </si>
+  <si>
+    <t>Card_Illust_131</t>
+  </si>
+  <si>
+    <t>Card_Illust_132</t>
+  </si>
+  <si>
     <t>Card_Effect_133</t>
+  </si>
+  <si>
+    <t>Card_Illust_133</t>
+  </si>
+  <si>
+    <t>Card_Illust_134</t>
   </si>
   <si>
     <t>Card_Mana_Arrow_Enhanced</t>
@@ -1396,7 +1468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DE9BD8-D0E7-41D4-A330-01F3591885DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B44827A-23AB-4637-A21C-AF113AD31A5E}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1634,7 +1706,7 @@
         <v>295</v>
       </c>
       <c r="S4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1693,7 +1765,7 @@
         <v>297</v>
       </c>
       <c r="S5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -1752,7 +1824,7 @@
         <v>295</v>
       </c>
       <c r="S6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -1811,7 +1883,7 @@
         <v>295</v>
       </c>
       <c r="S7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -1867,10 +1939,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="S8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -1926,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="S9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -1955,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1985,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>303</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
+        <v>307</v>
+      </c>
+      <c r="S10" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -2014,7 +2086,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -2044,10 +2116,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>303</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
+        <v>307</v>
+      </c>
+      <c r="S11" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -2103,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="S12" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2162,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="S13" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -2224,7 +2296,7 @@
         <v>295</v>
       </c>
       <c r="S14" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -2283,7 +2355,7 @@
         <v>295</v>
       </c>
       <c r="S15" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -2339,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="S16" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -2398,10 +2470,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="S17" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -2457,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="S18" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -2516,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="S19" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -2575,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="S20" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -2634,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="S21" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -2663,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -2693,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="S22" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -2722,7 +2794,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2752,10 +2824,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="S23" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -2813,8 +2885,8 @@
       <c r="R24" t="s">
         <v>295</v>
       </c>
-      <c r="S24">
-        <v>0</v>
+      <c r="S24" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -2870,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>316</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="S25" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -2929,10 +3001,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>317</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
+        <v>331</v>
+      </c>
+      <c r="S26" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -2990,8 +3062,8 @@
       <c r="R27">
         <v>0</v>
       </c>
-      <c r="S27">
-        <v>0</v>
+      <c r="S27" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -3049,8 +3121,8 @@
       <c r="R28">
         <v>0</v>
       </c>
-      <c r="S28">
-        <v>0</v>
+      <c r="S28" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -3108,8 +3180,8 @@
       <c r="R29">
         <v>0</v>
       </c>
-      <c r="S29">
-        <v>0</v>
+      <c r="S29" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -3135,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="I30">
         <v>3</v>
@@ -3165,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>316</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="S30" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -3194,7 +3266,7 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="I31">
         <v>3</v>
@@ -3224,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>316</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="S31" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -3285,8 +3357,8 @@
       <c r="R32" t="s">
         <v>295</v>
       </c>
-      <c r="S32">
-        <v>0</v>
+      <c r="S32" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -3344,8 +3416,8 @@
       <c r="R33" t="s">
         <v>295</v>
       </c>
-      <c r="S33">
-        <v>0</v>
+      <c r="S33" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -3401,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>320</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
+        <v>342</v>
+      </c>
+      <c r="S34" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -3460,10 +3532,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>320</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
+        <v>342</v>
+      </c>
+      <c r="S35" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -3607,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -3666,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -3843,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -3902,7 +3974,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="I43">
         <v>1</v>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D1CBE00-0021-4EB2-B714-DB496B76E42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BF624E6-9D66-4A71-AD3B-8C5B9F8B08C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C3A60B2D-63B0-435B-B6D3-5132FC6FB1AD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{086F484D-1E6C-4816-AA44-B9A83380C30B}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -1468,8 +1468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B44827A-23AB-4637-A21C-AF113AD31A5E}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A34EF8-922D-4786-A11C-55AE02AA2501}">
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1747,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1806,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -1865,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="N7">
         <v>0</v>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BF624E6-9D66-4A71-AD3B-8C5B9F8B08C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2BA4E8-148E-4509-A40D-A278C5935FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{086F484D-1E6C-4816-AA44-B9A83380C30B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4C43E225-AE07-46B5-837A-1109AE495B87}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -1468,7 +1468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A34EF8-922D-4786-A11C-55AE02AA2501}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7784F7CF-BFF8-4609-8FC1-41B24D9D68D1}">
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1808,7 +1808,7 @@
         <v>123</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1867,7 +1867,7 @@
         <v>123</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="O7">
         <v>0</v>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2BA4E8-148E-4509-A40D-A278C5935FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BC5090-B3EA-4135-935D-546E32B3313D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4C43E225-AE07-46B5-837A-1109AE495B87}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{501F5ED8-335E-4169-A392-C147631FEF9A}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -1468,7 +1468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7784F7CF-BFF8-4609-8FC1-41B24D9D68D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A157C0-76DC-48BF-A906-570D99BC2DA2}">
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N21">
         <v>0</v>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BC5090-B3EA-4135-935D-546E32B3313D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3181B683-7CBE-4880-9E91-42F84611D041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{501F5ED8-335E-4169-A392-C147631FEF9A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6293C294-93F9-4D09-A4ED-1ECDD2A4363C}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -128,19 +128,19 @@
     <t>Card_CrossChisel</t>
   </si>
   <si>
-    <t>Card_Cross Chisel_Name</t>
-  </si>
-  <si>
-    <t>Card_Cross Chisel_Des</t>
+    <t>Card_Cross_Chisel_Name</t>
+  </si>
+  <si>
+    <t>Card_Cross_Chisel_Des</t>
   </si>
   <si>
     <t>Card_CrossChisel_Enhanced</t>
   </si>
   <si>
-    <t>Card_Cross Chisel_Enhanced_Name</t>
-  </si>
-  <si>
-    <t>Card_Cross Chisel_Enhanced_Des</t>
+    <t>Card_Cross_Chisel_Enhanced_Name</t>
+  </si>
+  <si>
+    <t>Card_Cross_Chisel_Enhanced_Des</t>
   </si>
   <si>
     <t>Card_Pickaxe</t>
@@ -236,19 +236,19 @@
     <t>Card_LargeScissors</t>
   </si>
   <si>
-    <t>Card_Large Scissors_Name</t>
-  </si>
-  <si>
-    <t>Card_Large Scissors_Des</t>
+    <t>Card_Large_Scissors_Name</t>
+  </si>
+  <si>
+    <t>Card_Large_Scissors_Des</t>
   </si>
   <si>
     <t>Card_LargeScissors_Enhanced</t>
   </si>
   <si>
-    <t>Card_Large Scissors_Enhanced_Name</t>
-  </si>
-  <si>
-    <t>Card_Large Scissors_Enhanced_Des</t>
+    <t>Card_Large_Scissors_Enhanced_Name</t>
+  </si>
+  <si>
+    <t>Card_Large_Scissors_Enhanced_Des</t>
   </si>
   <si>
     <t>Card_WeakeningNormal</t>
@@ -1468,7 +1468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A157C0-76DC-48BF-A906-570D99BC2DA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271A70B3-0F25-4AB0-82FE-A44074261B5C}">
   <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{059F0A5A-4B01-40E0-8BAB-CD2FD0BE2AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2366D2DD-E447-4B6D-B310-AB2C05BB6944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6458AC5F-BC70-4338-89BC-E8649974D22F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="9405" windowHeight="15585" xr2:uid="{9DF4F4A0-09AC-4583-B606-61AF292C9D37}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="234">
   <si>
     <t>ID</t>
   </si>
@@ -429,6 +429,78 @@
   </si>
   <si>
     <t>Card_Dummy_401_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_1</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_1_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_1_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_2</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_2_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_2_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_3</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_3_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_3_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_4</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_4_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_4_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_5</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_5_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_5_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_6</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_6_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_6_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_7</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_7_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_7_Name_Des</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_8</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_8_Name</t>
+  </si>
+  <si>
+    <t>Card_Add_Test_8_Name_Des</t>
   </si>
   <si>
     <t>Card_type</t>
@@ -1051,8 +1123,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80409670-777B-4E2C-828E-B4746653C3C4}">
-  <dimension ref="A1:S43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D82624-449C-4909-83A4-762A3AEBDA01}">
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1069,49 +1141,49 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="F1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="G1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="H1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="I1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="J1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="K1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="L1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="M1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="N1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="O1" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="P1" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="Q1" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="R1" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="S1" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1167,10 +1239,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S2" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1226,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="S3" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1285,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S4" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1329,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1344,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="S5" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -1388,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1403,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S6" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -1447,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1462,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S7" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -1521,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S8" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -1580,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S9" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -1609,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1639,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="S10" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -1668,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -1698,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="S11" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -1757,10 +1829,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="S12" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -1816,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="S13" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -1875,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S14" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -1934,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S15" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -1993,10 +2065,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="S16" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -2052,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="S17" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -2111,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="S18" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
@@ -2170,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="S19" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
@@ -2214,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2229,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S20" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -2273,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2288,10 +2360,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S21" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
@@ -2317,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -2347,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="S22" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
@@ -2376,7 +2448,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -2406,10 +2478,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="S23" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
@@ -2450,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -2465,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S24" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -2509,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -2524,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="S25" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -2568,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -2583,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="S26" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -2645,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
@@ -2704,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
@@ -2763,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
@@ -2789,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="I30">
         <v>3</v>
@@ -2804,13 +2876,13 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -2819,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="S30" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
@@ -2848,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="I31">
         <v>3</v>
@@ -2863,13 +2935,13 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -2878,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="S31" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
@@ -2922,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -2937,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S32" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
@@ -2981,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -2996,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S33" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
@@ -3040,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -3055,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="S34" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
@@ -3099,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -3114,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="S35" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
@@ -3173,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="S36" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
@@ -3232,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="S37" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
@@ -3291,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="S38" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
@@ -3350,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="S39" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
@@ -3409,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="S40" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
@@ -3468,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="S41" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
@@ -3527,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="S42" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
@@ -3586,10 +3658,482 @@
         <v>0</v>
       </c>
       <c r="R43" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="S43" t="s">
-        <v>209</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>32</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>103</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44" t="s">
+        <v>169</v>
+      </c>
+      <c r="S44" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>104</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45" t="s">
+        <v>169</v>
+      </c>
+      <c r="S45" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>145</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>139</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>32</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>106</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>169</v>
+      </c>
+      <c r="S46" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>146</v>
+      </c>
+      <c r="B47" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47" t="s">
+        <v>136</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>32</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>111</v>
+      </c>
+      <c r="N47">
+        <v>107</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>169</v>
+      </c>
+      <c r="S47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>147</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>145</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>32</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>108</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="s">
+        <v>169</v>
+      </c>
+      <c r="S48" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>148</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>32</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>109</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49" t="s">
+        <v>169</v>
+      </c>
+      <c r="S49" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>149</v>
+      </c>
+      <c r="B50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>3</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>151</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>32</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>110</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50" t="s">
+        <v>169</v>
+      </c>
+      <c r="S50" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>150</v>
+      </c>
+      <c r="B51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51" t="s">
+        <v>148</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>32</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>112</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51" t="s">
+        <v>169</v>
+      </c>
+      <c r="S51" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Plan/Table/LiveData/02.CardData.xlsx
+++ b/Plan/Table/LiveData/02.CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2366D2DD-E447-4B6D-B310-AB2C05BB6944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3753F612-067E-4263-83D5-D1942467612D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="9405" windowHeight="15585" xr2:uid="{9DF4F4A0-09AC-4583-B606-61AF292C9D37}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="14610" windowHeight="15585" xr2:uid="{A9BFAFD4-9DD8-4F20-A561-F2FA2E3B0524}"/>
   </bookViews>
   <sheets>
     <sheet name="02.CardData" sheetId="1" r:id="rId1"/>
@@ -1123,7 +1123,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D82624-449C-4909-83A4-762A3AEBDA01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711E600A-4274-4637-91CA-F7D450C88792}">
   <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3696,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="K44">
-        <v>32</v>
+        <v>957</v>
       </c>
       <c r="L44">
         <v>0</v>
